--- a/class test/class test 11/Test Record.xlsx
+++ b/class test/class test 11/Test Record.xlsx
@@ -1,41 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 11/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="122" documentId="11_68DF1BED38F31E1694601FE51815821B40A2AD41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AAFEC87-B0A7-4D05-918A-C1AF2260223E}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>ARUN ARYA</t>
+  </si>
+  <si>
+    <t>MANSI</t>
+  </si>
+  <si>
+    <t>PRIYANSHU PANDEY</t>
+  </si>
+  <si>
+    <t>PRIYANSHU KANDPAL</t>
+  </si>
+  <si>
+    <t>AYUSH ROY</t>
+  </si>
+  <si>
+    <t>DIKSHANT</t>
+  </si>
+  <si>
+    <t>KARAN</t>
+  </si>
+  <si>
+    <t>KARTIKEY</t>
+  </si>
+  <si>
+    <t>ISHANT</t>
+  </si>
+  <si>
+    <t>PRANAY SATI</t>
+  </si>
+  <si>
+    <t>PARAS SATI</t>
+  </si>
+  <si>
+    <t>ADITYA NEGI</t>
+  </si>
+  <si>
+    <t>NEHA NEGI</t>
+  </si>
+  <si>
+    <t>JANVI</t>
+  </si>
+  <si>
+    <t>MANAS BHAGAT</t>
+  </si>
+  <si>
+    <t>ab</t>
+  </si>
+  <si>
+    <t>RAJAT ADHIKARI</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>SPARSH DUBEY</t>
+  </si>
+  <si>
+    <t>GAURAV KUMAR</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>ch1</t>
+  </si>
+  <si>
+    <t>ch2</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>ch3</t>
+  </si>
+  <si>
+    <t>ch4</t>
+  </si>
+  <si>
+    <t>ch5</t>
+  </si>
+  <si>
+    <t>ch 6</t>
+  </si>
+  <si>
+    <t>PRAVEEN RAUTELA</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -52,7 +133,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +141,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,278 +502,524 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="7.4140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>NAME</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Ch3 (MM:20)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Ch4 (MM:20)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Ch5 (MM:20)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ARUN ARYA</v>
-      </c>
-      <c r="B2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46182</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46199</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46218</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46220</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2">
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1">
+        <v>4</v>
+      </c>
+      <c r="G4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1">
         <v>13</v>
       </c>
-      <c r="D2">
+      <c r="F5" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>MANSI</v>
-      </c>
-      <c r="B3">
+      <c r="G5" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>6</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1">
         <v>8</v>
       </c>
-      <c r="C3">
+      <c r="E7" s="1">
         <v>12</v>
       </c>
-      <c r="D3">
+      <c r="F7" s="1">
+        <v>16</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>6</v>
+      </c>
+      <c r="E9" s="1">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1">
+        <v>12</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1">
+        <v>12</v>
+      </c>
+      <c r="G10" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1">
+        <v>9</v>
+      </c>
+      <c r="G11" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="1">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PRIYANSHU PANDEY</v>
-      </c>
-      <c r="B4">
+      <c r="G13" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="C4">
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1">
+        <v>19</v>
+      </c>
+      <c r="F15" s="1">
+        <v>18</v>
+      </c>
+      <c r="G15" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
         <v>13</v>
       </c>
-      <c r="D4">
+      <c r="D16" s="1">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1">
+        <v>9</v>
+      </c>
+      <c r="G16" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1">
+        <v>12</v>
+      </c>
+      <c r="G17" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PRIYANSHU KANDPAL</v>
-      </c>
-      <c r="B5">
+      <c r="C18" s="1">
+        <v>5</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1">
+        <v>8</v>
+      </c>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1">
+        <v>7</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="1">
+        <v>12</v>
+      </c>
+      <c r="F19" s="1">
+        <v>8</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="1">
+        <v>5</v>
+      </c>
+      <c r="F20" s="1">
+        <v>14</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="C5">
-        <v>17</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>AYUSH ROY</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>DIKSHANT</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>12</v>
-      </c>
-      <c r="D7">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>KARAN</v>
-      </c>
-      <c r="B8">
+      <c r="G22" s="1">
         <v>3</v>
       </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>KARTIKEY</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>14</v>
-      </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ISHANT</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>PRANAY SATI</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>17</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>PARAS SATI</v>
-      </c>
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>19</v>
-      </c>
-      <c r="D12">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>ADITYA NEGI</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>6</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>NEHA NEGI</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>JANVI</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>8</v>
-      </c>
-      <c r="D15">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>MANAS BHAGAT</v>
-      </c>
-      <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="C16" t="str">
-        <v>ab</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>RAJAT ADHIKARI</v>
-      </c>
-      <c r="B17" t="str">
-        <v>AB</v>
-      </c>
-      <c r="C17">
-        <v>12</v>
-      </c>
-      <c r="D17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>SPARSH DUBEY</v>
-      </c>
-      <c r="B18" t="str">
-        <v>AB</v>
-      </c>
-      <c r="C18">
-        <v>5</v>
-      </c>
-      <c r="D18">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>GAURAV KUMAR</v>
-      </c>
-      <c r="B19" t="str">
-        <v>AB</v>
-      </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19" t="str">
-        <v>ab</v>
-      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D19"/>
+    <ignoredError sqref="A1 A5 D5:F5 D15:F15 A15 D22:F22 A22 A19:A20 D19:F20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/class test/class test 11/Test Record.xlsx
+++ b/class test/class test 11/Test Record.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="11_68DF1BED38F31E1694601FE51815821B40A2AD41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AAFEC87-B0A7-4D05-918A-C1AF2260223E}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="11_68DF1BED38F31E1694601FE51815821B40A2AD41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D19818-10ED-4986-84CA-61667674B1DC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CT" sheetId="1" r:id="rId1"/>
+    <sheet name="PT" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
   <si>
     <t>NAME</t>
   </si>
@@ -110,6 +111,12 @@
   </si>
   <si>
     <t>PRAVEEN RAUTELA</t>
+  </si>
+  <si>
+    <t>ASHUTOSH</t>
+  </si>
+  <si>
+    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -133,7 +140,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -156,14 +163,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -179,6 +206,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1019,7 +1050,267 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1 A5 D5:F5 D15:F15 A15 D22:F22 A22 A19:A20 D19:F20" numberStoredAsText="1"/>
+    <ignoredError sqref="A5 D5:F5 D15:F15 A15 D22:F22 A22 A19:A20 D19:F20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85DFBCA-4A27-4C76-818E-208E0880957F}">
+  <dimension ref="A3:C25"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="18.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>17</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="1">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:B25">
+    <sortCondition ref="B6:B25"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/class test/class test 11/Test Record.xlsx
+++ b/class test/class test 11/Test Record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="11_68DF1BED38F31E1694601FE51815821B40A2AD41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D19818-10ED-4986-84CA-61667674B1DC}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="11_68DF1BED38F31E1694601FE51815821B40A2AD41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A940D6D8-F072-4E62-AC12-9F45E68A63DA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CT" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="32">
   <si>
     <t>NAME</t>
   </si>
@@ -180,11 +180,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -534,42 +533,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="7.4140625" customWidth="1"/>
+    <col min="2" max="2" width="18.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="7.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" s="1">
-        <v>20</v>
       </c>
       <c r="C2" s="1">
         <v>20</v>
@@ -586,36 +582,39 @@
       <c r="G2" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="H2" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="2">
+      <c r="C3" s="2">
         <v>46150</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>46182</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>46199</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>46218</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>46220</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>46241</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -624,434 +623,517 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1">
         <v>6</v>
-      </c>
-      <c r="F4" s="1">
-        <v>4</v>
       </c>
       <c r="G4" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="H4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C5" s="1">
         <v>12</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <v>11</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>12</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>13</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>11</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>6</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="C8" s="1">
         <v>11</v>
       </c>
-      <c r="C7" s="1">
+      <c r="D8" s="1">
         <v>7</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E8" s="1">
         <v>8</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F8" s="1">
         <v>12</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G8" s="1">
         <v>16</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H8" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1">
+      <c r="C10" s="1">
         <v>0</v>
       </c>
-      <c r="C8" s="1">
+      <c r="D10" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H10" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1">
+      <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="C9" s="1">
+      <c r="D11" s="1">
         <v>5</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F11" s="1">
         <v>8</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G11" s="1">
         <v>12</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1">
+      <c r="C12" s="1">
         <v>4</v>
       </c>
-      <c r="C10" s="1">
+      <c r="D12" s="1">
         <v>6</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E12" s="1">
         <v>3</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F12" s="1">
         <v>6</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G12" s="1">
         <v>12</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H12" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F13" s="1">
         <v>14</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G13" s="1">
         <v>9</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H13" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="1">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1">
-        <v>11</v>
-      </c>
-      <c r="G13" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="1">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G14" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="H14" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>9</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="1">
+      <c r="H15" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1">
         <v>6</v>
       </c>
-      <c r="C15" s="1">
+      <c r="D17" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E17" s="1">
         <v>10</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F17" s="1">
         <v>19</v>
       </c>
-      <c r="F15" s="1">
-        <v>18</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="G17" s="1">
+        <v>18</v>
+      </c>
+      <c r="H17" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="1">
+      <c r="C18" s="1">
         <v>4</v>
       </c>
-      <c r="C16" s="1">
+      <c r="D18" s="1">
         <v>13</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E18" s="1">
         <v>4</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F18" s="1">
         <v>17</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G18" s="1">
         <v>9</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H18" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F20" s="1">
         <v>17</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G20" s="1">
         <v>12</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H20" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="1">
+      <c r="C21" s="1">
         <v>8</v>
       </c>
-      <c r="C18" s="1">
+      <c r="D21" s="1">
         <v>5</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F21" s="1">
         <v>13</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G21" s="1">
         <v>8</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H21" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="1">
+      <c r="C22" s="1">
         <v>7</v>
       </c>
-      <c r="C19" s="1">
+      <c r="D22" s="1">
         <v>5</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="E22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="1">
         <v>12</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G22" s="1">
         <v>8</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+      <c r="H22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="1">
         <v>5</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G23" s="1">
         <v>14</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="1">
-        <v>3</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="1">
-        <v>3</v>
+      <c r="H23" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:H23">
+    <sortCondition ref="B4:B23"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A5 D5:F5 D15:F15 A15 D22:F22 A22 A19:A20 D19:F20" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1064,10 +1146,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1113,7 +1195,7 @@
       <c r="A8">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="1">

--- a/class test/class test 11/Test Record.xlsx
+++ b/class test/class test 11/Test Record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="11_68DF1BED38F31E1694601FE51815821B40A2AD41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A940D6D8-F072-4E62-AC12-9F45E68A63DA}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="11_68DF1BED38F31E1694601FE51815821B40A2AD41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90B00B64-C424-4161-A724-CDB2AAAB68BE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>NAME</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>PT</t>
+  </si>
+  <si>
+    <t>ch7</t>
   </si>
 </sst>
 </file>
@@ -533,14 +536,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18.58203125" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="7.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,8 +565,11 @@
       <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
@@ -585,8 +591,11 @@
       <c r="H2" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
@@ -608,8 +617,11 @@
       <c r="H3" s="2">
         <v>46241</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" s="2">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -634,8 +646,11 @@
       <c r="H4" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -660,8 +675,11 @@
       <c r="H5" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -686,8 +704,11 @@
       <c r="H6" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
@@ -712,8 +733,11 @@
       <c r="H7" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
@@ -738,8 +762,11 @@
       <c r="H8" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -764,8 +791,11 @@
       <c r="H9" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
@@ -790,8 +820,11 @@
       <c r="H10" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
@@ -816,8 +849,9 @@
       <c r="H11" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
@@ -842,8 +876,11 @@
       <c r="H12" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
@@ -868,8 +905,11 @@
       <c r="H13" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
@@ -894,8 +934,11 @@
       <c r="H14" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
@@ -920,8 +963,11 @@
       <c r="H15" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
@@ -946,8 +992,11 @@
       <c r="H16" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
@@ -972,8 +1021,11 @@
       <c r="H17" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
@@ -998,8 +1050,11 @@
       <c r="H18" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1024,8 +1079,11 @@
       <c r="H19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1050,8 +1108,11 @@
       <c r="H20" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1076,8 +1137,9 @@
       <c r="H21" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1102,8 +1164,11 @@
       <c r="H22" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1127,6 +1192,9 @@
       </c>
       <c r="H23" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="I23" s="1">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
